--- a/CRM_Gantt_Chart_9_Weeks.xlsx
+++ b/CRM_Gantt_Chart_9_Weeks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Matrial\CRM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB26715-19B4-4332-A038-67EDF1EEBA57}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED23880-81A9-44E0-A652-023DD4520767}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,16 +67,16 @@
     <t>Lead Management</t>
   </si>
   <si>
-    <t>Dashboard</t>
-  </si>
-  <si>
-    <t>Team Leader</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
     <t>Logs &amp; Notifications System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team Leader </t>
+  </si>
+  <si>
+    <t>Dashbourd</t>
   </si>
 </sst>
 </file>
@@ -554,7 +554,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3">
         <v>5</v>
@@ -577,7 +577,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B5" s="3">
         <v>6</v>
@@ -600,7 +600,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B6" s="3">
         <v>7</v>
@@ -623,7 +623,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" s="3">
         <v>8</v>
